--- a/insumos/01_estimaciones/Reporte_06_mayo_2025.xlsx
+++ b/insumos/01_estimaciones/Reporte_06_mayo_2025.xlsx
@@ -16,12 +16,12 @@
     <sheet name="resultado_REMUNTOT" sheetId="2" r:id="rId2"/>
     <sheet name="resultado_TTT" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="45">
   <si>
     <t>dominio</t>
   </si>
@@ -154,11 +154,17 @@
   <si>
     <t>Zonas no delimitadas</t>
   </si>
+  <si>
+    <t>Galápagos</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -176,12 +182,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -211,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -226,6 +238,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.21875" bestFit="1" customWidth="1"/>
@@ -2034,6 +2055,59 @@
         <v>14.181656984275721</v>
       </c>
     </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="7">
+        <v>22.810919075140401</v>
+      </c>
+      <c r="C29" s="7">
+        <v>0.96842452857191497</v>
+      </c>
+      <c r="D29" s="7">
+        <v>20.91190333832516</v>
+      </c>
+      <c r="E29" s="7">
+        <v>24.70993481195563</v>
+      </c>
+      <c r="F29" s="7">
+        <v>0.93784606753973576</v>
+      </c>
+      <c r="G29" s="7">
+        <v>4.245442831048904E-2</v>
+      </c>
+      <c r="H29" s="7">
+        <v>2.1717145965008</v>
+      </c>
+      <c r="I29" s="8">
+        <v>484824.91714208393</v>
+      </c>
+      <c r="J29" s="8">
+        <v>70340.695506633012</v>
+      </c>
+      <c r="K29" s="8">
+        <v>21254.072032128319</v>
+      </c>
+      <c r="L29" s="8">
+        <v>2714.4853820286339</v>
+      </c>
+      <c r="M29" s="8">
+        <v>17161</v>
+      </c>
+      <c r="N29" s="8">
+        <v>778</v>
+      </c>
+      <c r="O29" s="7">
+        <v>348.74172212929562</v>
+      </c>
+      <c r="P29" s="7">
+        <v>20.402247463361121</v>
+      </c>
+      <c r="Q29" s="7">
+        <v>18.674627764142869</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
